--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120223873</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,4673 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120401005</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>566165</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7041903</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120401435</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566231</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7041870</v>
+      </c>
+      <c r="S4" t="n">
+        <v>18</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120401576</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566265</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7041855</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120402025</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566305</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7041870</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120400587</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566217</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7041938</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120401611</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566320</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7041829</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120400668</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566208</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7041926</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120400774</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566156</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7041952</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120402309</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>566429</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7041911</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120400823</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566192</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7041854</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120401967</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>566372</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7041865</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120400930</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>566189</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7041814</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120401222</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>566262</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7041805</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120401533</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>566262</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7041874</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120400619</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>566213</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7041932</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120400940</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>566193</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7041818</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120400718</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>566210</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7041934</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120402380</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>566319</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7041924</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120401775</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>566335</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7041823</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120400879</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>566169</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7041936</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120400926</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>566184</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7041933</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120401175</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>566246</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7041822</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120402161</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96885</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>566335</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7041879</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120402260</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>566363</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7041890</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120402053</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>566368</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7041869</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120401361</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>566269</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7041804</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120400985</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>566208</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7041813</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120401365</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>566218</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7041867</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120401399</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>566283</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7041823</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120401447</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>566289</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7041805</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120401966</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>566312</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7041864</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120402365</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>566394</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7041907</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120401125</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>566239</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7041810</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120400817</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>566168</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7041948</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120401710</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>566277</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7041856</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120402098</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>566323</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7041866</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120401527</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>566291</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7041822</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120401135</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>566175</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7041859</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120400694</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>566206</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7041916</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120401165</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>566196</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7041827</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -1136,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120402025</v>
+        <v>120400587</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1152,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566305</v>
+        <v>566217</v>
       </c>
       <c r="R6" t="n">
-        <v>7041870</v>
+        <v>7041938</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120400587</v>
+        <v>120402025</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1264,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566217</v>
+        <v>566305</v>
       </c>
       <c r="R7" t="n">
-        <v>7041938</v>
+        <v>7041870</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1333,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,12 +1353,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400985</v>
+        <v>120401365</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3826,38 +3826,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566208</v>
+        <v>566218</v>
       </c>
       <c r="R29" t="n">
-        <v>7041813</v>
+        <v>7041867</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3889,7 +3898,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3899,7 +3908,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3926,10 +3935,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120401365</v>
+        <v>120400985</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3938,47 +3947,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566218</v>
+        <v>566208</v>
       </c>
       <c r="R30" t="n">
-        <v>7041867</v>
+        <v>7041813</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120401005</v>
+        <v>120400930</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566165</v>
+        <v>566189</v>
       </c>
       <c r="R3" t="n">
-        <v>7041903</v>
+        <v>7041814</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,19 +887,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120401435</v>
+        <v>120400823</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -938,7 +934,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566231</v>
+        <v>566192</v>
       </c>
       <c r="R4" t="n">
-        <v>7041870</v>
+        <v>7041854</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120401576</v>
+        <v>120401967</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566265</v>
+        <v>566372</v>
       </c>
       <c r="R5" t="n">
-        <v>7041855</v>
+        <v>7041865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120400587</v>
+        <v>120401775</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,38 +1144,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566217</v>
+        <v>566335</v>
       </c>
       <c r="R6" t="n">
-        <v>7041938</v>
+        <v>7041823</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120402025</v>
+        <v>120400694</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1260,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566305</v>
+        <v>566206</v>
       </c>
       <c r="R7" t="n">
-        <v>7041870</v>
+        <v>7041916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,12 +1342,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1369,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401611</v>
+        <v>120402365</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1405,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566320</v>
+        <v>566394</v>
       </c>
       <c r="R8" t="n">
-        <v>7041829</v>
+        <v>7041907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,7 +1481,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120400668</v>
+        <v>120401527</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1512,7 +1516,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1521,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566208</v>
+        <v>566291</v>
       </c>
       <c r="R9" t="n">
-        <v>7041926</v>
+        <v>7041822</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120400774</v>
+        <v>120400879</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1628,7 +1632,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566156</v>
+        <v>566169</v>
       </c>
       <c r="R10" t="n">
-        <v>7041952</v>
+        <v>7041936</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120402309</v>
+        <v>120401435</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,41 +1725,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566429</v>
+        <v>566231</v>
       </c>
       <c r="R11" t="n">
-        <v>7041911</v>
+        <v>7041870</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,19 +1822,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120400823</v>
+        <v>120401135</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1856,12 +1869,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1870,10 +1878,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566192</v>
+        <v>566175</v>
       </c>
       <c r="R12" t="n">
-        <v>7041854</v>
+        <v>7041859</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1915,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,22 +1938,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401967</v>
+        <v>120400774</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,38 +1962,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566372</v>
+        <v>566156</v>
       </c>
       <c r="R13" t="n">
-        <v>7041865</v>
+        <v>7041952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2017,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2027,7 +2039,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2054,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400930</v>
+        <v>120402098</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,38 +2078,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566189</v>
+        <v>566323</v>
       </c>
       <c r="R14" t="n">
-        <v>7041814</v>
+        <v>7041866</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2129,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2139,7 +2160,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,10 +2187,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120401222</v>
+        <v>120401710</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,38 +2199,52 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566262</v>
+        <v>566277</v>
       </c>
       <c r="R15" t="n">
-        <v>7041805</v>
+        <v>7041856</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2251,12 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,19 +2301,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120401533</v>
+        <v>120402380</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2318,7 +2348,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2332,10 +2362,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566262</v>
+        <v>566319</v>
       </c>
       <c r="R16" t="n">
-        <v>7041874</v>
+        <v>7041924</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2367,7 +2397,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2377,7 +2407,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400619</v>
+        <v>120402161</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,47 +2446,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566213</v>
+        <v>566335</v>
       </c>
       <c r="R17" t="n">
-        <v>7041932</v>
+        <v>7041879</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2509,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2519,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,7 +2546,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400940</v>
+        <v>120401533</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2560,7 +2581,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2574,10 +2595,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566193</v>
+        <v>566262</v>
       </c>
       <c r="R18" t="n">
-        <v>7041818</v>
+        <v>7041874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2630,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2640,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,10 +2667,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400718</v>
+        <v>120400926</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,38 +2679,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566210</v>
+        <v>566184</v>
       </c>
       <c r="R19" t="n">
-        <v>7041934</v>
+        <v>7041933</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,7 +2746,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2756,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2758,10 +2783,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120402380</v>
+        <v>120401399</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2770,47 +2795,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566319</v>
+        <v>566283</v>
       </c>
       <c r="R20" t="n">
-        <v>7041924</v>
+        <v>7041823</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2842,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2852,7 +2868,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,19 +2883,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120401775</v>
+        <v>120400619</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2914,7 +2930,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2923,10 +2944,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566335</v>
+        <v>566213</v>
       </c>
       <c r="R21" t="n">
-        <v>7041823</v>
+        <v>7041932</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2979,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2989,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2983,22 +3004,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120400879</v>
+        <v>120401447</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,42 +3028,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566169</v>
+        <v>566289</v>
       </c>
       <c r="R22" t="n">
-        <v>7041936</v>
+        <v>7041805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3101,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,10 +3128,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400926</v>
+        <v>120401222</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,42 +3140,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566184</v>
+        <v>566262</v>
       </c>
       <c r="R23" t="n">
-        <v>7041933</v>
+        <v>7041805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3190,7 +3203,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3200,7 +3213,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120401175</v>
+        <v>120401966</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,31 +3257,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3272,10 +3294,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566246</v>
+        <v>566312</v>
       </c>
       <c r="R24" t="n">
-        <v>7041822</v>
+        <v>7041864</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3307,7 +3329,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3317,12 +3339,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3349,10 +3366,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120402161</v>
+        <v>120401361</v>
       </c>
       <c r="B25" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,38 +3378,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566335</v>
+        <v>566269</v>
       </c>
       <c r="R25" t="n">
-        <v>7041879</v>
+        <v>7041804</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,7 +3445,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3434,7 +3455,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3449,22 +3470,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120402260</v>
+        <v>120401611</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3473,47 +3494,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566363</v>
+        <v>566320</v>
       </c>
       <c r="R26" t="n">
-        <v>7041890</v>
+        <v>7041829</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3545,7 +3557,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3555,7 +3567,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3570,12 +3582,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3698,10 +3710,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120401361</v>
+        <v>120401165</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,30 +3722,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3742,10 +3755,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566269</v>
+        <v>566196</v>
       </c>
       <c r="R28" t="n">
-        <v>7041804</v>
+        <v>7041827</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3777,7 +3790,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3787,7 +3800,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3814,7 +3827,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120401365</v>
+        <v>120400940</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3849,7 +3862,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3863,10 +3876,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566218</v>
+        <v>566193</v>
       </c>
       <c r="R29" t="n">
-        <v>7041867</v>
+        <v>7041818</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3898,7 +3911,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3908,7 +3921,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3935,10 +3948,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400985</v>
+        <v>120401005</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3947,38 +3960,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566208</v>
+        <v>566165</v>
       </c>
       <c r="R30" t="n">
-        <v>7041813</v>
+        <v>7041903</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4010,7 +4027,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4020,7 +4037,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4035,22 +4052,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120401399</v>
+        <v>120402025</v>
       </c>
       <c r="B31" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4063,21 +4080,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4087,10 +4104,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566283</v>
+        <v>566305</v>
       </c>
       <c r="R31" t="n">
-        <v>7041823</v>
+        <v>7041870</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4122,7 +4139,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4132,7 +4149,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4147,22 +4169,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120401447</v>
+        <v>120400587</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4175,21 +4197,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4199,10 +4221,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566289</v>
+        <v>566217</v>
       </c>
       <c r="R32" t="n">
-        <v>7041805</v>
+        <v>7041938</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4234,7 +4256,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4244,7 +4266,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4271,10 +4293,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120401966</v>
+        <v>120401576</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4283,47 +4305,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566312</v>
+        <v>566265</v>
       </c>
       <c r="R33" t="n">
-        <v>7041864</v>
+        <v>7041855</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4355,7 +4368,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4365,7 +4378,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4392,10 +4405,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120402365</v>
+        <v>120401125</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4408,34 +4421,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566394</v>
+        <v>566239</v>
       </c>
       <c r="R34" t="n">
-        <v>7041907</v>
+        <v>7041810</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4467,7 +4485,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4477,7 +4495,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4492,19 +4510,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120401125</v>
+        <v>120401175</v>
       </c>
       <c r="B35" t="n">
         <v>57320</v>
@@ -4549,10 +4567,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566239</v>
+        <v>566246</v>
       </c>
       <c r="R35" t="n">
-        <v>7041810</v>
+        <v>7041822</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4584,7 +4602,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4594,7 +4612,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4621,7 +4644,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400817</v>
+        <v>120400668</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4656,7 +4679,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4665,10 +4688,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566168</v>
+        <v>566208</v>
       </c>
       <c r="R36" t="n">
-        <v>7041948</v>
+        <v>7041926</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4700,7 +4723,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4710,7 +4733,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4737,10 +4760,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120401710</v>
+        <v>120400718</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4749,52 +4772,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566277</v>
+        <v>566210</v>
       </c>
       <c r="R37" t="n">
-        <v>7041856</v>
+        <v>7041934</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4826,7 +4835,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4836,7 +4845,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4851,22 +4860,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120402098</v>
+        <v>120400985</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4875,47 +4884,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566323</v>
+        <v>566208</v>
       </c>
       <c r="R38" t="n">
-        <v>7041866</v>
+        <v>7041813</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4984,7 +4984,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120401527</v>
+        <v>120400817</v>
       </c>
       <c r="B39" t="n">
         <v>97930</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566291</v>
+        <v>566168</v>
       </c>
       <c r="R39" t="n">
-        <v>7041822</v>
+        <v>7041948</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5100,7 +5100,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120401135</v>
+        <v>120401365</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -5135,7 +5135,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5144,10 +5149,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566175</v>
+        <v>566218</v>
       </c>
       <c r="R40" t="n">
-        <v>7041859</v>
+        <v>7041867</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5204,22 +5209,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120400694</v>
+        <v>120402309</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5228,47 +5233,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566206</v>
+        <v>566429</v>
       </c>
       <c r="R41" t="n">
-        <v>7041916</v>
+        <v>7041911</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5300,7 +5296,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5310,7 +5306,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5325,22 +5321,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120401165</v>
+        <v>120402260</v>
       </c>
       <c r="B42" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5349,31 +5345,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566196</v>
+        <v>566363</v>
       </c>
       <c r="R42" t="n">
-        <v>7041827</v>
+        <v>7041890</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5442,12 +5442,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -3594,10 +3594,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120402053</v>
+        <v>120401165</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3606,30 +3606,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3638,10 +3639,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566368</v>
+        <v>566196</v>
       </c>
       <c r="R27" t="n">
-        <v>7041869</v>
+        <v>7041827</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3673,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3683,7 +3684,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3710,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120401165</v>
+        <v>120400940</v>
       </c>
       <c r="B28" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3722,31 +3723,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3755,10 +3760,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566196</v>
+        <v>566193</v>
       </c>
       <c r="R28" t="n">
-        <v>7041827</v>
+        <v>7041818</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3790,7 +3795,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3800,7 +3805,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3815,19 +3820,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400940</v>
+        <v>120401005</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3862,12 +3867,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3876,10 +3876,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566193</v>
+        <v>566165</v>
       </c>
       <c r="R29" t="n">
-        <v>7041818</v>
+        <v>7041903</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3936,19 +3936,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120401005</v>
+        <v>120402053</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3992,10 +3992,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566165</v>
+        <v>566368</v>
       </c>
       <c r="R30" t="n">
-        <v>7041903</v>
+        <v>7041869</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120400930</v>
+        <v>120400940</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566189</v>
+        <v>566193</v>
       </c>
       <c r="R3" t="n">
-        <v>7041814</v>
+        <v>7041818</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120400823</v>
+        <v>120400985</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,47 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566192</v>
+        <v>566208</v>
       </c>
       <c r="R4" t="n">
-        <v>7041854</v>
+        <v>7041813</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120401967</v>
+        <v>120400718</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566372</v>
+        <v>566210</v>
       </c>
       <c r="R5" t="n">
-        <v>7041865</v>
+        <v>7041934</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120401775</v>
+        <v>120401365</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1170,16 +1170,21 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566335</v>
+        <v>566218</v>
       </c>
       <c r="R6" t="n">
-        <v>7041823</v>
+        <v>7041867</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,19 +1241,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120400694</v>
+        <v>120401361</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1283,12 +1288,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566206</v>
+        <v>566269</v>
       </c>
       <c r="R7" t="n">
-        <v>7041916</v>
+        <v>7041804</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,22 +1357,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120402365</v>
+        <v>120401967</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566394</v>
+        <v>566372</v>
       </c>
       <c r="R8" t="n">
-        <v>7041907</v>
+        <v>7041865</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120401527</v>
+        <v>120401175</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,30 +1493,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1525,7 +1526,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566291</v>
+        <v>566246</v>
       </c>
       <c r="R9" t="n">
         <v>7041822</v>
@@ -1560,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1571,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,19 +1591,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120400879</v>
+        <v>120401435</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1632,7 +1638,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1641,13 +1652,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566169</v>
+        <v>566231</v>
       </c>
       <c r="R10" t="n">
-        <v>7041936</v>
+        <v>7041870</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1686,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,19 +1712,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120401435</v>
+        <v>120401005</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1748,12 +1759,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1762,13 +1768,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566231</v>
+        <v>566165</v>
       </c>
       <c r="R11" t="n">
-        <v>7041870</v>
+        <v>7041903</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,19 +1828,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120401135</v>
+        <v>120402098</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1872,16 +1878,21 @@
           <t>40</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566175</v>
+        <v>566323</v>
       </c>
       <c r="R12" t="n">
-        <v>7041859</v>
+        <v>7041866</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,22 +1949,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400774</v>
+        <v>120400587</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,42 +1973,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566156</v>
+        <v>566217</v>
       </c>
       <c r="R13" t="n">
-        <v>7041952</v>
+        <v>7041938</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120402098</v>
+        <v>120401399</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,47 +2085,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566323</v>
+        <v>566283</v>
       </c>
       <c r="R14" t="n">
-        <v>7041866</v>
+        <v>7041823</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,19 +2173,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120401710</v>
+        <v>120401775</v>
       </c>
       <c r="B15" t="n">
         <v>97930</v>
@@ -2225,26 +2223,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566277</v>
+        <v>566335</v>
       </c>
       <c r="R15" t="n">
-        <v>7041856</v>
+        <v>7041823</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2264,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2274,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,22 +2289,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120402380</v>
+        <v>120402161</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,47 +2313,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566319</v>
+        <v>566335</v>
       </c>
       <c r="R16" t="n">
-        <v>7041924</v>
+        <v>7041879</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,7 +2376,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2407,7 +2386,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2434,10 +2413,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120402161</v>
+        <v>120401533</v>
       </c>
       <c r="B17" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2446,38 +2425,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566335</v>
+        <v>566262</v>
       </c>
       <c r="R17" t="n">
-        <v>7041879</v>
+        <v>7041874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2509,7 +2497,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2519,7 +2507,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2546,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120401533</v>
+        <v>120401576</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,47 +2546,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566262</v>
+        <v>566265</v>
       </c>
       <c r="R18" t="n">
-        <v>7041874</v>
+        <v>7041855</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2630,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2640,7 +2619,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,10 +2646,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400926</v>
+        <v>120401611</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,42 +2658,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566184</v>
+        <v>566320</v>
       </c>
       <c r="R19" t="n">
-        <v>7041933</v>
+        <v>7041829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2746,7 +2721,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2756,7 +2731,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2783,10 +2758,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120401399</v>
+        <v>120400817</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,38 +2770,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566283</v>
+        <v>566168</v>
       </c>
       <c r="R20" t="n">
-        <v>7041823</v>
+        <v>7041948</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2858,7 +2837,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2868,7 +2847,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,7 +2874,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120400619</v>
+        <v>120401527</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2933,21 +2912,16 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566213</v>
+        <v>566291</v>
       </c>
       <c r="R21" t="n">
-        <v>7041932</v>
+        <v>7041822</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2979,7 +2953,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2989,7 +2963,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,22 +2978,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120401447</v>
+        <v>120400879</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3028,38 +3002,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566289</v>
+        <v>566169</v>
       </c>
       <c r="R22" t="n">
-        <v>7041805</v>
+        <v>7041936</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3091,7 +3069,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,7 +3079,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3128,10 +3106,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120401222</v>
+        <v>120402260</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3140,38 +3118,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566262</v>
+        <v>566363</v>
       </c>
       <c r="R23" t="n">
-        <v>7041805</v>
+        <v>7041890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3203,7 +3190,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3213,12 +3200,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3233,22 +3215,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120401966</v>
+        <v>120402025</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3257,47 +3239,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566312</v>
+        <v>566305</v>
       </c>
       <c r="R24" t="n">
-        <v>7041864</v>
+        <v>7041870</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3329,7 +3302,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3339,7 +3312,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,7 +3344,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120401361</v>
+        <v>120402380</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3401,7 +3379,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3410,10 +3393,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566269</v>
+        <v>566319</v>
       </c>
       <c r="R25" t="n">
-        <v>7041804</v>
+        <v>7041924</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3445,7 +3428,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3455,7 +3438,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3470,22 +3453,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120401611</v>
+        <v>120401135</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3494,38 +3477,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566320</v>
+        <v>566175</v>
       </c>
       <c r="R26" t="n">
-        <v>7041829</v>
+        <v>7041859</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3557,7 +3544,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3567,7 +3554,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3711,10 +3698,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400940</v>
+        <v>120400930</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,47 +3710,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566193</v>
+        <v>566189</v>
       </c>
       <c r="R28" t="n">
-        <v>7041818</v>
+        <v>7041814</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3795,7 +3773,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3805,7 +3783,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,7 +3810,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120401005</v>
+        <v>120400619</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3867,7 +3845,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3876,10 +3859,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566165</v>
+        <v>566213</v>
       </c>
       <c r="R29" t="n">
-        <v>7041903</v>
+        <v>7041932</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3911,7 +3894,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3921,7 +3904,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3936,19 +3919,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120402053</v>
+        <v>120400694</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3983,7 +3966,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3992,10 +3980,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566368</v>
+        <v>566206</v>
       </c>
       <c r="R30" t="n">
-        <v>7041869</v>
+        <v>7041916</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4027,7 +4015,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4037,7 +4025,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4052,22 +4040,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120402025</v>
+        <v>120401710</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4076,38 +4064,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566305</v>
+        <v>566277</v>
       </c>
       <c r="R31" t="n">
-        <v>7041870</v>
+        <v>7041856</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4139,7 +4141,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4149,12 +4151,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4181,10 +4178,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120400587</v>
+        <v>120401966</v>
       </c>
       <c r="B32" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4193,38 +4190,47 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566217</v>
+        <v>566312</v>
       </c>
       <c r="R32" t="n">
-        <v>7041938</v>
+        <v>7041864</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4256,7 +4262,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4266,7 +4272,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4281,22 +4287,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120401576</v>
+        <v>120402309</v>
       </c>
       <c r="B33" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4309,21 +4315,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4333,10 +4339,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566265</v>
+        <v>566429</v>
       </c>
       <c r="R33" t="n">
-        <v>7041855</v>
+        <v>7041911</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4368,7 +4374,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4378,7 +4384,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4393,22 +4399,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120401125</v>
+        <v>120401447</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4421,39 +4427,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566239</v>
+        <v>566289</v>
       </c>
       <c r="R34" t="n">
-        <v>7041810</v>
+        <v>7041805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4485,7 +4486,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4495,7 +4496,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4510,22 +4511,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120401175</v>
+        <v>120402365</v>
       </c>
       <c r="B35" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4538,39 +4539,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566246</v>
+        <v>566394</v>
       </c>
       <c r="R35" t="n">
-        <v>7041822</v>
+        <v>7041907</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4602,7 +4598,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4612,12 +4608,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4632,19 +4623,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400668</v>
+        <v>120400926</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4679,7 +4670,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4688,10 +4679,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566208</v>
+        <v>566184</v>
       </c>
       <c r="R36" t="n">
-        <v>7041926</v>
+        <v>7041933</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4723,7 +4714,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4733,7 +4724,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4760,10 +4751,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120400718</v>
+        <v>120402053</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4772,38 +4763,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566210</v>
+        <v>566368</v>
       </c>
       <c r="R37" t="n">
-        <v>7041934</v>
+        <v>7041869</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4835,7 +4830,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4845,7 +4840,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4872,10 +4867,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400985</v>
+        <v>120400774</v>
       </c>
       <c r="B38" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4884,38 +4879,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566208</v>
+        <v>566156</v>
       </c>
       <c r="R38" t="n">
-        <v>7041813</v>
+        <v>7041952</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4947,7 +4946,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4957,7 +4956,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4972,22 +4971,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120400817</v>
+        <v>120401125</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4996,30 +4995,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5028,10 +5028,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566168</v>
+        <v>566239</v>
       </c>
       <c r="R39" t="n">
-        <v>7041948</v>
+        <v>7041810</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,22 +5088,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120401365</v>
+        <v>120401222</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5112,47 +5112,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566218</v>
+        <v>566262</v>
       </c>
       <c r="R40" t="n">
-        <v>7041867</v>
+        <v>7041805</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5184,7 +5175,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5194,7 +5185,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5209,22 +5205,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120402309</v>
+        <v>120400668</v>
       </c>
       <c r="B41" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5233,38 +5229,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566429</v>
+        <v>566208</v>
       </c>
       <c r="R41" t="n">
-        <v>7041911</v>
+        <v>7041926</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120402260</v>
+        <v>120400823</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566363</v>
+        <v>566192</v>
       </c>
       <c r="R42" t="n">
-        <v>7041890</v>
+        <v>7041854</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120400940</v>
+        <v>120400718</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,47 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566193</v>
+        <v>566210</v>
       </c>
       <c r="R3" t="n">
-        <v>7041818</v>
+        <v>7041934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120400985</v>
+        <v>120402053</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566208</v>
+        <v>566368</v>
       </c>
       <c r="R4" t="n">
-        <v>7041813</v>
+        <v>7041869</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +988,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120400718</v>
+        <v>120400823</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1027,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566210</v>
+        <v>566192</v>
       </c>
       <c r="R5" t="n">
-        <v>7041934</v>
+        <v>7041854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1124,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120401365</v>
+        <v>120401447</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,47 +1148,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566218</v>
+        <v>566289</v>
       </c>
       <c r="R6" t="n">
-        <v>7041867</v>
+        <v>7041805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1221,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401361</v>
+        <v>120401967</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,42 +1260,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566269</v>
+        <v>566372</v>
       </c>
       <c r="R7" t="n">
-        <v>7041804</v>
+        <v>7041865</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,7 +1333,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401967</v>
+        <v>120400774</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,38 +1372,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566372</v>
+        <v>566156</v>
       </c>
       <c r="R8" t="n">
-        <v>7041865</v>
+        <v>7041952</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120401175</v>
+        <v>120401966</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,31 +1488,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1526,10 +1525,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566246</v>
+        <v>566312</v>
       </c>
       <c r="R9" t="n">
-        <v>7041822</v>
+        <v>7041864</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,12 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120401435</v>
+        <v>120401175</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,35 +1609,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1652,13 +1642,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566231</v>
+        <v>566246</v>
       </c>
       <c r="R10" t="n">
-        <v>7041870</v>
+        <v>7041822</v>
       </c>
       <c r="S10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1687,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,7 +1719,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120401005</v>
+        <v>120402098</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1759,7 +1754,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566165</v>
+        <v>566323</v>
       </c>
       <c r="R11" t="n">
-        <v>7041903</v>
+        <v>7041866</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,19 +1828,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120402098</v>
+        <v>120401527</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1875,12 +1875,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1889,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566323</v>
+        <v>566291</v>
       </c>
       <c r="R12" t="n">
-        <v>7041866</v>
+        <v>7041822</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,22 +1944,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400587</v>
+        <v>120400985</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,21 +1972,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,10 +1996,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566217</v>
+        <v>566208</v>
       </c>
       <c r="R13" t="n">
-        <v>7041938</v>
+        <v>7041813</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2036,7 +2031,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2041,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,22 +2056,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120401399</v>
+        <v>120401222</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,21 +2084,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566283</v>
+        <v>566262</v>
       </c>
       <c r="R14" t="n">
-        <v>7041823</v>
+        <v>7041805</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2143,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2153,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120401775</v>
+        <v>120401576</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,42 +2197,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566335</v>
+        <v>566265</v>
       </c>
       <c r="R15" t="n">
-        <v>7041823</v>
+        <v>7041855</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2264,7 +2260,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2274,7 +2270,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,22 +2285,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120402161</v>
+        <v>120401611</v>
       </c>
       <c r="B16" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,25 +2309,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2341,10 +2337,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566335</v>
+        <v>566320</v>
       </c>
       <c r="R16" t="n">
-        <v>7041879</v>
+        <v>7041829</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,7 +2372,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2382,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,22 +2397,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120401533</v>
+        <v>120401165</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,35 +2421,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2462,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566262</v>
+        <v>566196</v>
       </c>
       <c r="R17" t="n">
-        <v>7041874</v>
+        <v>7041827</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2507,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,22 +2514,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120401576</v>
+        <v>120400940</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2546,38 +2538,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566265</v>
+        <v>566193</v>
       </c>
       <c r="R18" t="n">
-        <v>7041855</v>
+        <v>7041818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2610,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,7 +2620,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,10 +2647,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120401611</v>
+        <v>120400587</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2662,21 +2663,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2686,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566320</v>
+        <v>566217</v>
       </c>
       <c r="R19" t="n">
-        <v>7041829</v>
+        <v>7041938</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2731,7 +2732,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2758,7 +2759,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120400817</v>
+        <v>120401365</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2796,16 +2797,21 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566168</v>
+        <v>566218</v>
       </c>
       <c r="R20" t="n">
-        <v>7041948</v>
+        <v>7041867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2837,7 +2843,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2847,7 +2853,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,19 +2868,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120401527</v>
+        <v>120401361</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2909,7 +2915,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2918,10 +2924,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566291</v>
+        <v>566269</v>
       </c>
       <c r="R21" t="n">
-        <v>7041822</v>
+        <v>7041804</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2953,7 +2959,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2963,7 +2969,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,10 +2996,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120400879</v>
+        <v>120402025</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3002,42 +3008,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566169</v>
+        <v>566305</v>
       </c>
       <c r="R22" t="n">
-        <v>7041936</v>
+        <v>7041870</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3069,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3079,7 +3081,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3094,19 +3101,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120402260</v>
+        <v>120400668</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3141,12 +3148,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3155,10 +3157,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566363</v>
+        <v>566208</v>
       </c>
       <c r="R23" t="n">
-        <v>7041890</v>
+        <v>7041926</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3190,7 +3192,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3200,7 +3202,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3215,22 +3217,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120402025</v>
+        <v>120400926</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3239,38 +3241,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566305</v>
+        <v>566184</v>
       </c>
       <c r="R24" t="n">
-        <v>7041870</v>
+        <v>7041933</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3302,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3312,12 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,19 +3333,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120402380</v>
+        <v>120400879</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3379,12 +3380,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3393,10 +3389,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566319</v>
+        <v>566169</v>
       </c>
       <c r="R25" t="n">
-        <v>7041924</v>
+        <v>7041936</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3428,7 +3424,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3438,7 +3434,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3453,19 +3449,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120401135</v>
+        <v>120401775</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3500,7 +3496,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3509,10 +3505,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566175</v>
+        <v>566335</v>
       </c>
       <c r="R26" t="n">
-        <v>7041859</v>
+        <v>7041823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3544,7 +3540,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3554,7 +3550,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3581,10 +3577,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120401165</v>
+        <v>120402161</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3593,43 +3589,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566196</v>
+        <v>566335</v>
       </c>
       <c r="R27" t="n">
-        <v>7041827</v>
+        <v>7041879</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3661,7 +3652,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3671,7 +3662,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3686,12 +3677,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3810,10 +3801,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120400619</v>
+        <v>120401125</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3822,35 +3813,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3859,10 +3846,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566213</v>
+        <v>566239</v>
       </c>
       <c r="R29" t="n">
-        <v>7041932</v>
+        <v>7041810</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3894,7 +3881,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3904,7 +3891,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3931,7 +3918,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120400694</v>
+        <v>120402260</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3966,7 +3953,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3980,10 +3967,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566206</v>
+        <v>566363</v>
       </c>
       <c r="R30" t="n">
-        <v>7041916</v>
+        <v>7041890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4015,7 +4002,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4025,7 +4012,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4178,10 +4165,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120401966</v>
+        <v>120402309</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4190,47 +4177,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566312</v>
+        <v>566429</v>
       </c>
       <c r="R32" t="n">
-        <v>7041864</v>
+        <v>7041911</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4262,7 +4240,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4272,7 +4250,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4287,22 +4265,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120402309</v>
+        <v>120400817</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4311,38 +4289,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566429</v>
+        <v>566168</v>
       </c>
       <c r="R33" t="n">
-        <v>7041911</v>
+        <v>7041948</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4374,7 +4356,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4384,7 +4366,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4411,10 +4393,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120401447</v>
+        <v>120401135</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4423,38 +4405,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566289</v>
+        <v>566175</v>
       </c>
       <c r="R34" t="n">
-        <v>7041805</v>
+        <v>7041859</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4486,7 +4472,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4496,7 +4482,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4523,10 +4509,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120402365</v>
+        <v>120401435</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4535,41 +4521,50 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566394</v>
+        <v>566231</v>
       </c>
       <c r="R35" t="n">
-        <v>7041907</v>
+        <v>7041870</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4598,7 +4593,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4608,7 +4603,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4623,22 +4618,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400926</v>
+        <v>120402365</v>
       </c>
       <c r="B36" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4647,42 +4642,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566184</v>
+        <v>566394</v>
       </c>
       <c r="R36" t="n">
-        <v>7041933</v>
+        <v>7041907</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4714,7 +4705,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4724,7 +4715,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4751,7 +4742,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120402053</v>
+        <v>120402380</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4786,7 +4777,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4795,10 +4791,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566368</v>
+        <v>566319</v>
       </c>
       <c r="R37" t="n">
-        <v>7041869</v>
+        <v>7041924</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4830,7 +4826,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4840,7 +4836,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4855,19 +4851,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400774</v>
+        <v>120400694</v>
       </c>
       <c r="B38" t="n">
         <v>97930</v>
@@ -4902,7 +4898,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4911,10 +4912,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566156</v>
+        <v>566206</v>
       </c>
       <c r="R38" t="n">
-        <v>7041952</v>
+        <v>7041916</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4946,7 +4947,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4956,7 +4957,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,22 +4972,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120401125</v>
+        <v>120401399</v>
       </c>
       <c r="B39" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4999,39 +5000,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566239</v>
+        <v>566283</v>
       </c>
       <c r="R39" t="n">
-        <v>7041810</v>
+        <v>7041823</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5063,7 +5059,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5073,7 +5069,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5088,22 +5084,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120401222</v>
+        <v>120401005</v>
       </c>
       <c r="B40" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5112,38 +5108,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566262</v>
+        <v>566165</v>
       </c>
       <c r="R40" t="n">
-        <v>7041805</v>
+        <v>7041903</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5185,12 +5185,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5217,7 +5212,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120400668</v>
+        <v>120401533</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -5252,7 +5247,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566208</v>
+        <v>566262</v>
       </c>
       <c r="R41" t="n">
-        <v>7041926</v>
+        <v>7041874</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5321,19 +5321,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120400823</v>
+        <v>120400619</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566192</v>
+        <v>566213</v>
       </c>
       <c r="R42" t="n">
-        <v>7041854</v>
+        <v>7041932</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -1956,10 +1956,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120400985</v>
+        <v>120401222</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,21 +1972,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566208</v>
+        <v>566262</v>
       </c>
       <c r="R13" t="n">
-        <v>7041813</v>
+        <v>7041805</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2041,7 +2041,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,22 +2061,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120401222</v>
+        <v>120400985</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,21 +2089,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2108,10 +2113,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566262</v>
+        <v>566208</v>
       </c>
       <c r="R14" t="n">
-        <v>7041805</v>
+        <v>7041813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2143,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2153,12 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,12 +2173,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120400718</v>
+        <v>120400823</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566210</v>
+        <v>566192</v>
       </c>
       <c r="R3" t="n">
-        <v>7041934</v>
+        <v>7041854</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120402053</v>
+        <v>120402161</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566368</v>
+        <v>566335</v>
       </c>
       <c r="R4" t="n">
-        <v>7041869</v>
+        <v>7041879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120400823</v>
+        <v>120400985</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,47 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566192</v>
+        <v>566208</v>
       </c>
       <c r="R5" t="n">
-        <v>7041854</v>
+        <v>7041813</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120401447</v>
+        <v>120401222</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1176,7 +1172,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566289</v>
+        <v>566262</v>
       </c>
       <c r="R6" t="n">
         <v>7041805</v>
@@ -1211,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,7 +1217,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120401967</v>
+        <v>120400774</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,38 +1261,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566372</v>
+        <v>566156</v>
       </c>
       <c r="R7" t="n">
-        <v>7041865</v>
+        <v>7041952</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120400774</v>
+        <v>120401005</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1395,7 +1400,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1404,10 +1409,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566156</v>
+        <v>566165</v>
       </c>
       <c r="R8" t="n">
-        <v>7041952</v>
+        <v>7041903</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120401966</v>
+        <v>120401576</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1488,47 +1493,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566312</v>
+        <v>566265</v>
       </c>
       <c r="R9" t="n">
-        <v>7041864</v>
+        <v>7041855</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1560,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,10 +1593,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120401175</v>
+        <v>120402260</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,31 +1605,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566246</v>
+        <v>566363</v>
       </c>
       <c r="R10" t="n">
-        <v>7041822</v>
+        <v>7041890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,12 +1687,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,7 +1714,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120402098</v>
+        <v>120401361</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1754,12 +1749,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1768,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566323</v>
+        <v>566269</v>
       </c>
       <c r="R11" t="n">
-        <v>7041866</v>
+        <v>7041804</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1803,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,12 +1818,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1956,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401222</v>
+        <v>120401447</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,21 +1962,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1996,7 +1986,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566262</v>
+        <v>566289</v>
       </c>
       <c r="R13" t="n">
         <v>7041805</v>
@@ -2031,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2041,12 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2058,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400985</v>
+        <v>120400718</v>
       </c>
       <c r="B14" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,21 +2074,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2113,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566208</v>
+        <v>566210</v>
       </c>
       <c r="R14" t="n">
-        <v>7041813</v>
+        <v>7041934</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,22 +2158,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120401576</v>
+        <v>120401611</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,21 +2186,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2225,10 +2210,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566265</v>
+        <v>566320</v>
       </c>
       <c r="R15" t="n">
-        <v>7041855</v>
+        <v>7041829</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,7 +2245,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2255,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,22 +2270,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120401611</v>
+        <v>120400587</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,21 +2298,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2337,10 +2322,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566320</v>
+        <v>566217</v>
       </c>
       <c r="R16" t="n">
-        <v>7041829</v>
+        <v>7041938</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2357,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2382,7 +2367,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120401165</v>
+        <v>120401967</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,39 +2410,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566196</v>
+        <v>566372</v>
       </c>
       <c r="R17" t="n">
-        <v>7041827</v>
+        <v>7041865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2489,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2479,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120400940</v>
+        <v>120401399</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,47 +2518,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566193</v>
+        <v>566283</v>
       </c>
       <c r="R18" t="n">
-        <v>7041818</v>
+        <v>7041823</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2620,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,22 +2606,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400587</v>
+        <v>120402025</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2663,21 +2634,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2687,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566217</v>
+        <v>566305</v>
       </c>
       <c r="R19" t="n">
-        <v>7041938</v>
+        <v>7041870</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2722,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2732,7 +2703,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,22 +2723,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120401365</v>
+        <v>120401175</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2771,35 +2747,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2808,10 +2780,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566218</v>
+        <v>566246</v>
       </c>
       <c r="R20" t="n">
-        <v>7041867</v>
+        <v>7041822</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2843,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2853,7 +2825,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,7 +2857,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120401361</v>
+        <v>120401135</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2915,7 +2892,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2924,10 +2901,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566269</v>
+        <v>566175</v>
       </c>
       <c r="R21" t="n">
-        <v>7041804</v>
+        <v>7041859</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2959,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2969,7 +2946,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,10 +2973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120402025</v>
+        <v>120401435</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3008,41 +2985,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566305</v>
+        <v>566231</v>
       </c>
       <c r="R22" t="n">
         <v>7041870</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3071,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,12 +3067,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3113,10 +3094,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120400668</v>
+        <v>120401165</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3125,30 +3106,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3157,10 +3139,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566208</v>
+        <v>566196</v>
       </c>
       <c r="R23" t="n">
-        <v>7041926</v>
+        <v>7041827</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3192,7 +3174,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3202,7 +3184,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3229,7 +3211,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400926</v>
+        <v>120400668</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3264,7 +3246,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3273,10 +3255,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566184</v>
+        <v>566208</v>
       </c>
       <c r="R24" t="n">
-        <v>7041933</v>
+        <v>7041926</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,7 +3290,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3300,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,7 +3327,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400879</v>
+        <v>120400926</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3380,7 +3362,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3389,10 +3371,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566169</v>
+        <v>566184</v>
       </c>
       <c r="R25" t="n">
-        <v>7041936</v>
+        <v>7041933</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,7 +3406,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3434,7 +3416,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,7 +3443,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120401775</v>
+        <v>120400940</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3496,7 +3478,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3505,10 +3492,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566335</v>
+        <v>566193</v>
       </c>
       <c r="R26" t="n">
-        <v>7041823</v>
+        <v>7041818</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3540,7 +3527,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3550,7 +3537,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3565,22 +3552,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120402161</v>
+        <v>120402365</v>
       </c>
       <c r="B27" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3589,25 +3576,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3617,10 +3604,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566335</v>
+        <v>566394</v>
       </c>
       <c r="R27" t="n">
-        <v>7041879</v>
+        <v>7041907</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,7 +3639,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3662,7 +3649,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,22 +3664,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400930</v>
+        <v>120400879</v>
       </c>
       <c r="B28" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3701,38 +3688,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566189</v>
+        <v>566169</v>
       </c>
       <c r="R28" t="n">
-        <v>7041814</v>
+        <v>7041936</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3764,7 +3755,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3774,7 +3765,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3789,22 +3780,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120401125</v>
+        <v>120401710</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3813,31 +3804,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566239</v>
+        <v>566277</v>
       </c>
       <c r="R29" t="n">
-        <v>7041810</v>
+        <v>7041856</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,7 +3918,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120402260</v>
+        <v>120401966</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566363</v>
+        <v>566312</v>
       </c>
       <c r="R30" t="n">
-        <v>7041890</v>
+        <v>7041864</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4039,7 +4039,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120401710</v>
+        <v>120400817</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4077,26 +4077,16 @@
           <t>10</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566277</v>
+        <v>566168</v>
       </c>
       <c r="R31" t="n">
-        <v>7041856</v>
+        <v>7041948</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4128,7 +4118,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4138,7 +4128,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4153,22 +4143,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120402309</v>
+        <v>120401125</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4181,34 +4171,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566429</v>
+        <v>566239</v>
       </c>
       <c r="R32" t="n">
-        <v>7041911</v>
+        <v>7041810</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4240,7 +4235,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4250,7 +4245,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4265,22 +4260,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120400817</v>
+        <v>120400930</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4289,42 +4284,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566168</v>
+        <v>566189</v>
       </c>
       <c r="R33" t="n">
-        <v>7041948</v>
+        <v>7041814</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4356,7 +4347,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4366,7 +4357,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4381,19 +4372,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120401135</v>
+        <v>120401775</v>
       </c>
       <c r="B34" t="n">
         <v>97930</v>
@@ -4428,7 +4419,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4437,10 +4428,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566175</v>
+        <v>566335</v>
       </c>
       <c r="R34" t="n">
-        <v>7041859</v>
+        <v>7041823</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4472,7 +4463,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4482,7 +4473,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4509,7 +4500,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120401435</v>
+        <v>120401365</v>
       </c>
       <c r="B35" t="n">
         <v>97930</v>
@@ -4544,7 +4535,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4558,13 +4549,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566231</v>
+        <v>566218</v>
       </c>
       <c r="R35" t="n">
-        <v>7041870</v>
+        <v>7041867</v>
       </c>
       <c r="S35" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4593,7 +4584,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4603,7 +4594,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4630,10 +4621,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120402365</v>
+        <v>120402098</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4642,38 +4633,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566394</v>
+        <v>566323</v>
       </c>
       <c r="R36" t="n">
-        <v>7041907</v>
+        <v>7041866</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4730,12 +4730,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400694</v>
+        <v>120402309</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4875,47 +4875,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566206</v>
+        <v>566429</v>
       </c>
       <c r="R38" t="n">
-        <v>7041916</v>
+        <v>7041911</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4947,7 +4938,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4957,7 +4948,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4972,22 +4963,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120401399</v>
+        <v>120400619</v>
       </c>
       <c r="B39" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4996,38 +4987,47 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566283</v>
+        <v>566213</v>
       </c>
       <c r="R39" t="n">
-        <v>7041823</v>
+        <v>7041932</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5084,19 +5084,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120401005</v>
+        <v>120402053</v>
       </c>
       <c r="B40" t="n">
         <v>97930</v>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5140,10 +5140,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566165</v>
+        <v>566368</v>
       </c>
       <c r="R40" t="n">
-        <v>7041903</v>
+        <v>7041869</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5212,7 +5212,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120401533</v>
+        <v>120400694</v>
       </c>
       <c r="B41" t="n">
         <v>97930</v>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566262</v>
+        <v>566206</v>
       </c>
       <c r="R41" t="n">
-        <v>7041874</v>
+        <v>7041916</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120400619</v>
+        <v>120401533</v>
       </c>
       <c r="B42" t="n">
         <v>97930</v>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566213</v>
+        <v>566262</v>
       </c>
       <c r="R42" t="n">
-        <v>7041932</v>
+        <v>7041874</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120400823</v>
+        <v>120402260</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -822,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566192</v>
+        <v>566363</v>
       </c>
       <c r="R3" t="n">
-        <v>7041854</v>
+        <v>7041890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120402161</v>
+        <v>120401361</v>
       </c>
       <c r="B4" t="n">
-        <v>96885</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +920,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566335</v>
+        <v>566269</v>
       </c>
       <c r="R4" t="n">
-        <v>7041879</v>
+        <v>7041804</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1012,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120400985</v>
+        <v>120400774</v>
       </c>
       <c r="B5" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1036,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566208</v>
+        <v>566156</v>
       </c>
       <c r="R5" t="n">
-        <v>7041813</v>
+        <v>7041952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120401222</v>
+        <v>120400718</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566262</v>
+        <v>566210</v>
       </c>
       <c r="R6" t="n">
-        <v>7041805</v>
+        <v>7041934</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,12 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1252,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120400774</v>
+        <v>120402053</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1284,7 +1287,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1293,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566156</v>
+        <v>566368</v>
       </c>
       <c r="R7" t="n">
-        <v>7041952</v>
+        <v>7041869</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120401005</v>
+        <v>120401135</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1400,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1409,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566165</v>
+        <v>566175</v>
       </c>
       <c r="R8" t="n">
-        <v>7041903</v>
+        <v>7041859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1593,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120402260</v>
+        <v>120401125</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,35 +1608,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1642,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566363</v>
+        <v>566239</v>
       </c>
       <c r="R10" t="n">
-        <v>7041890</v>
+        <v>7041810</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1677,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1687,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120401361</v>
+        <v>120402161</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
+        <v>96885</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,42 +1725,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566269</v>
+        <v>566335</v>
       </c>
       <c r="R11" t="n">
-        <v>7041804</v>
+        <v>7041879</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,19 +1813,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120401527</v>
+        <v>120401435</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1865,7 +1860,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1874,13 +1874,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566291</v>
+        <v>566231</v>
       </c>
       <c r="R12" t="n">
-        <v>7041822</v>
+        <v>7041870</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,22 +1934,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120401447</v>
+        <v>120400694</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,38 +1958,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566289</v>
+        <v>566206</v>
       </c>
       <c r="R13" t="n">
-        <v>7041805</v>
+        <v>7041916</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2030,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,7 +2040,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,22 +2055,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120400718</v>
+        <v>120400926</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2070,38 +2079,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566210</v>
+        <v>566184</v>
       </c>
       <c r="R14" t="n">
-        <v>7041934</v>
+        <v>7041933</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2156,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120401611</v>
+        <v>120401775</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2182,38 +2195,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566320</v>
+        <v>566335</v>
       </c>
       <c r="R15" t="n">
-        <v>7041829</v>
+        <v>7041823</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2245,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2272,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,10 +2299,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120400587</v>
+        <v>120400940</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2294,38 +2311,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566217</v>
+        <v>566193</v>
       </c>
       <c r="R16" t="n">
-        <v>7041938</v>
+        <v>7041818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2357,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2367,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,22 +2408,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120401967</v>
+        <v>120400930</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2410,21 +2436,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2434,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566372</v>
+        <v>566189</v>
       </c>
       <c r="R17" t="n">
-        <v>7041865</v>
+        <v>7041814</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2469,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2479,7 +2505,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,22 +2520,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120401399</v>
+        <v>120401222</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2522,21 +2548,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2546,10 +2572,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566283</v>
+        <v>566262</v>
       </c>
       <c r="R18" t="n">
-        <v>7041823</v>
+        <v>7041805</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2591,7 +2617,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120402025</v>
+        <v>120400879</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,38 +2661,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566305</v>
+        <v>566169</v>
       </c>
       <c r="R19" t="n">
-        <v>7041870</v>
+        <v>7041936</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2693,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2703,12 +2738,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,22 +2753,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120401175</v>
+        <v>120401005</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2747,31 +2777,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2780,10 +2809,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566246</v>
+        <v>566165</v>
       </c>
       <c r="R20" t="n">
-        <v>7041822</v>
+        <v>7041903</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2844,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,12 +2854,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,19 +2869,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120401135</v>
+        <v>120401527</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -2892,7 +2916,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2901,10 +2925,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566175</v>
+        <v>566291</v>
       </c>
       <c r="R21" t="n">
-        <v>7041859</v>
+        <v>7041822</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,7 +2960,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,7 +2970,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,10 +2997,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120401435</v>
+        <v>120402365</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2985,50 +3009,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566231</v>
+        <v>566394</v>
       </c>
       <c r="R22" t="n">
-        <v>7041870</v>
+        <v>7041907</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3057,7 +3072,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3082,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3082,22 +3097,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120401165</v>
+        <v>120400619</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3106,31 +3121,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3139,10 +3158,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566196</v>
+        <v>566213</v>
       </c>
       <c r="R23" t="n">
-        <v>7041827</v>
+        <v>7041932</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3174,7 +3193,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3184,7 +3203,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,19 +3218,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120400668</v>
+        <v>120401533</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3246,7 +3265,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3255,10 +3279,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566208</v>
+        <v>566262</v>
       </c>
       <c r="R24" t="n">
-        <v>7041926</v>
+        <v>7041874</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3290,7 +3314,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3300,7 +3324,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,22 +3339,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120400926</v>
+        <v>120402025</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,42 +3363,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566184</v>
+        <v>566305</v>
       </c>
       <c r="R25" t="n">
-        <v>7041933</v>
+        <v>7041870</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,7 +3426,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,7 +3436,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3431,22 +3456,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120400940</v>
+        <v>120401175</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,35 +3480,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3492,10 +3513,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566193</v>
+        <v>566246</v>
       </c>
       <c r="R26" t="n">
-        <v>7041818</v>
+        <v>7041822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3527,7 +3548,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3537,7 +3558,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,10 +3590,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120402365</v>
+        <v>120400587</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,21 +3606,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3604,10 +3630,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566394</v>
+        <v>566217</v>
       </c>
       <c r="R27" t="n">
-        <v>7041907</v>
+        <v>7041938</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3639,7 +3665,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3675,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3676,7 +3702,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120400879</v>
+        <v>120401365</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3711,7 +3737,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3720,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566169</v>
+        <v>566218</v>
       </c>
       <c r="R28" t="n">
-        <v>7041936</v>
+        <v>7041867</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3755,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3765,7 +3796,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,19 +3811,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120401710</v>
+        <v>120402098</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3827,7 +3858,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3835,21 +3866,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566277</v>
+        <v>566323</v>
       </c>
       <c r="R29" t="n">
-        <v>7041856</v>
+        <v>7041866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3881,7 +3907,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3891,7 +3917,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3918,7 +3944,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120401966</v>
+        <v>120402380</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3953,7 +3979,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3967,10 +3993,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566312</v>
+        <v>566319</v>
       </c>
       <c r="R30" t="n">
-        <v>7041864</v>
+        <v>7041924</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4002,7 +4028,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4012,7 +4038,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4039,7 +4065,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120400817</v>
+        <v>120401966</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4074,7 +4100,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4083,10 +4114,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566168</v>
+        <v>566312</v>
       </c>
       <c r="R31" t="n">
-        <v>7041948</v>
+        <v>7041864</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4118,7 +4149,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4128,7 +4159,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4143,22 +4174,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120401125</v>
+        <v>120400817</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4167,31 +4198,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4200,10 +4230,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>566239</v>
+        <v>566168</v>
       </c>
       <c r="R32" t="n">
-        <v>7041810</v>
+        <v>7041948</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4235,7 +4265,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4245,7 +4275,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4260,22 +4290,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120400930</v>
+        <v>120401611</v>
       </c>
       <c r="B33" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4288,21 +4318,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4312,10 +4342,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>566189</v>
+        <v>566320</v>
       </c>
       <c r="R33" t="n">
-        <v>7041814</v>
+        <v>7041829</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4347,7 +4377,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4357,7 +4387,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4372,22 +4402,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120401775</v>
+        <v>120401165</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4396,30 +4426,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4428,10 +4459,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566335</v>
+        <v>566196</v>
       </c>
       <c r="R34" t="n">
-        <v>7041823</v>
+        <v>7041827</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4463,7 +4494,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4473,7 +4504,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4500,10 +4531,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120401365</v>
+        <v>120401967</v>
       </c>
       <c r="B35" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4512,47 +4543,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566218</v>
+        <v>566372</v>
       </c>
       <c r="R35" t="n">
-        <v>7041867</v>
+        <v>7041865</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4584,7 +4606,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4594,7 +4616,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4609,19 +4631,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120402098</v>
+        <v>120400668</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4656,12 +4678,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4670,10 +4687,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566323</v>
+        <v>566208</v>
       </c>
       <c r="R36" t="n">
-        <v>7041866</v>
+        <v>7041926</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4705,7 +4722,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4715,7 +4732,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4730,19 +4747,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120402380</v>
+        <v>120401710</v>
       </c>
       <c r="B37" t="n">
         <v>97930</v>
@@ -4777,7 +4794,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4785,16 +4802,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566319</v>
+        <v>566277</v>
       </c>
       <c r="R37" t="n">
-        <v>7041924</v>
+        <v>7041856</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4826,7 +4848,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4836,7 +4858,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4863,10 +4885,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120402309</v>
+        <v>120400823</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4875,38 +4897,47 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566429</v>
+        <v>566192</v>
       </c>
       <c r="R38" t="n">
-        <v>7041911</v>
+        <v>7041854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4938,7 +4969,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4948,7 +4979,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4963,22 +4994,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120400619</v>
+        <v>120401399</v>
       </c>
       <c r="B39" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4987,47 +5018,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>566213</v>
+        <v>566283</v>
       </c>
       <c r="R39" t="n">
-        <v>7041932</v>
+        <v>7041823</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5059,7 +5081,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5069,7 +5091,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5084,22 +5106,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120402053</v>
+        <v>120402309</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5108,42 +5130,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>566368</v>
+        <v>566429</v>
       </c>
       <c r="R40" t="n">
-        <v>7041869</v>
+        <v>7041911</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5175,7 +5193,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5185,7 +5203,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5212,10 +5230,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120400694</v>
+        <v>120400985</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5224,47 +5242,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>566206</v>
+        <v>566208</v>
       </c>
       <c r="R41" t="n">
-        <v>7041916</v>
+        <v>7041813</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5296,7 +5305,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5315,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5333,10 +5342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120401533</v>
+        <v>120401447</v>
       </c>
       <c r="B42" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5345,47 +5354,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>566262</v>
+        <v>566289</v>
       </c>
       <c r="R42" t="n">
-        <v>7041874</v>
+        <v>7041805</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5442,12 +5442,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 41506-2024 artfynd.xlsx
+++ b/artfynd/A 41506-2024 artfynd.xlsx
@@ -2420,10 +2420,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120400930</v>
+        <v>120400879</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,38 +2432,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566189</v>
+        <v>566169</v>
       </c>
       <c r="R17" t="n">
-        <v>7041814</v>
+        <v>7041936</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,12 +2524,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2649,10 +2653,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120400879</v>
+        <v>120400930</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2661,42 +2665,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566169</v>
+        <v>566189</v>
       </c>
       <c r="R19" t="n">
-        <v>7041936</v>
+        <v>7041814</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,12 +2753,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3702,7 +3702,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120401365</v>
+        <v>120402098</v>
       </c>
       <c r="B28" t="n">
         <v>97930</v>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566218</v>
+        <v>566323</v>
       </c>
       <c r="R28" t="n">
-        <v>7041867</v>
+        <v>7041866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3823,7 +3823,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120402098</v>
+        <v>120402380</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566323</v>
+        <v>566319</v>
       </c>
       <c r="R29" t="n">
-        <v>7041866</v>
+        <v>7041924</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3944,7 +3944,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120402380</v>
+        <v>120401966</v>
       </c>
       <c r="B30" t="n">
         <v>97930</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566319</v>
+        <v>566312</v>
       </c>
       <c r="R30" t="n">
-        <v>7041924</v>
+        <v>7041864</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4065,7 +4065,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120401966</v>
+        <v>120401365</v>
       </c>
       <c r="B31" t="n">
         <v>97930</v>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4114,10 +4114,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566312</v>
+        <v>566218</v>
       </c>
       <c r="R31" t="n">
-        <v>7041864</v>
+        <v>7041867</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4414,10 +4414,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120401165</v>
+        <v>120400668</v>
       </c>
       <c r="B34" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4426,31 +4426,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4459,10 +4458,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>566196</v>
+        <v>566208</v>
       </c>
       <c r="R34" t="n">
-        <v>7041827</v>
+        <v>7041926</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4494,7 +4493,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4504,7 +4503,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4531,10 +4530,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120401967</v>
+        <v>120401710</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4543,38 +4542,52 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>566372</v>
+        <v>566277</v>
       </c>
       <c r="R35" t="n">
-        <v>7041865</v>
+        <v>7041856</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4606,7 +4619,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4616,7 +4629,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4631,19 +4644,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120400668</v>
+        <v>120400823</v>
       </c>
       <c r="B36" t="n">
         <v>97930</v>
@@ -4678,7 +4691,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4687,10 +4705,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>566208</v>
+        <v>566192</v>
       </c>
       <c r="R36" t="n">
-        <v>7041926</v>
+        <v>7041854</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4722,7 +4740,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4732,7 +4750,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4747,22 +4765,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120401710</v>
+        <v>120401967</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4771,52 +4789,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>566277</v>
+        <v>566372</v>
       </c>
       <c r="R37" t="n">
-        <v>7041856</v>
+        <v>7041865</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4848,7 +4852,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4858,7 +4862,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4873,22 +4877,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120400823</v>
+        <v>120401165</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4897,35 +4901,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>566192</v>
+        <v>566196</v>
       </c>
       <c r="R38" t="n">
-        <v>7041854</v>
+        <v>7041827</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4994,12 +4994,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
